--- a/output/北塩原村_法定記載事項チェック.xlsx
+++ b/output/北塩原村_法定記載事項チェック.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,12 @@
     <font>
       <name val="游ゴシック"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="8">
@@ -115,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -155,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -905,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1666,10 +1675,142 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>本計画期間中に加わる記載事項（現在の告示には無いもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>加わる記載事項</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>施行の日</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>障がい福祉分野の扱い</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>当方の状態</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）。厚生労働省「社会福祉法等の一部を改正する法律の概要について」11頁</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>サービス量の中長期的な推計</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>令和9年4月1日</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>「※ 障害福祉分野においても同様の見直しを行う。」と明記されている。障がい福祉分野の施行の日は同資料に別に記載されていない</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>当方の推計は令和11年度まで。中長期の推計を持っていない。第5章1に、次期計画までに整えることと、介護保険事業計画の令和22年度（2040年度）を見据えた推計と同じ年次で揃えることを書いた（ＨＫ-1）。本計画に載せるか次期計画からかを県に確かめる（Ｍ-118・Ｓ-29）</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>将来に向けたサービス提供体制の確保に関する施策</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>令和9年4月1日</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>第5章2（必要な見込量の確保のための方策）が実質的に対応するが、「将来に向けた」＝本計画期間の後を見据えた記述にはなっていない。第5章1に、村内及び圏域の事業所が本計画期間の後も提供を続けられるかを毎年度確かめることを書いた（ＨＫ-1）</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>医療と介護の連携の状況等の勘案</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>令和9年4月1日</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>第7章3（高齢者福祉計画・介護保険事業計画との連携）と第5章2（15）医療へのアクセスで対応している。介護保険側への申し送りで版を固定して突合している</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>※ 基本指針（令和8年3月31日告示第4号）はまだこの改正を取り込んでいない。告示22項目の突合に混ぜると、告示にある事項と無い事項の区別が付かなくなるため別に置く。施行の日（令和9年4月1日）は第8期計画の期間の初日に当たる。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1838,7 +1979,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Ｍ-110</t>
         </is>

--- a/output/北塩原村_法定記載事項チェック.xlsx
+++ b/output/北塩原村_法定記載事項チェック.xlsx
@@ -593,7 +593,7 @@
     <row r="10" ht="62" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>6. 他メンバー版の記述は書き換えない。第1章5（4）は「本計画案を、令和９年２月８日～令和９年２月22日まで村ホームページ等で公開し、広く村民の方々から意見を募りました」と過去形で書いている。令和９年２月はまだ先であり、行われていない。素案の段階で確定版の体裁にしておく書き方と理解したため、当方は書き換えない。日程の確定と、確定時の時制の扱いを他メンバーに確かめる（Ｓ-27）。</t>
+          <t>6. 他メンバー版の記述のうち、日程は書き換えた。時制は書き換えない。第1章5（4）は「本計画案を、令和９年２月８日～令和９年２月22日まで村ホームページ等で公開し、広く村民の方々から意見を募りました」と書いていた。令和8年10月14日に工程を引き直したため（案Ａ）、日程を令和９年１月26日～令和９年２月９日（15日間）へ書き換えた（ＴＫ-4）。時制（「意見を募りました」と過去形で書いていること）は、素案の段階で確定版の体裁にしておく書き方と理解したため、当方は書き換えない。確定時の時制の扱いを他メンバーに確かめる（Ｓ-27）。</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>第1章5（4）の日付と時制</t>
+          <t>第1章5（4）の時制</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>第1章5（4）は「本計画案を、令和９年２月８日～令和９年２月22日まで村ホームページ等で公開し、広く村民の方々から意見を募りました」と過去形で書かれている。令和９年２月はまだ先であり、行われていない。素案の段階で確定版の体裁にしておく書き方と理解したため当方は書き換えていないが、①パブリックコメントの日程がこの日付で確定しているか②確定時に時制をそのままにするかを確かめたい。日程が動く場合は第1章5（4）と工程表の両方を直す</t>
+          <t>第1章5（4）は「本計画案を、令和９年２月８日～令和９年２月22日まで村ホームページ等で公開し、広く村民の方々から意見を募りました」と書かれていました。令和８年10月14日に工程を引き直したため（案Ａ）、日程を令和９年１月26日～令和９年２月９日（15日間）へ書き換えています（ＴＫ-4）。日程そのものは村への照会（Ｍ-125）に移しました。こちらでお伺いしたいのは時制の扱いです。「意見を募りました」と過去形で書かれていますが、令和９年１月はまだ先であり、行われていません。素案の段階で確定版の体裁にしておく書き方と理解したため当方は書き換えていません。①素案（策定委員会・パブリックコメントに出すもの）の段階では　過去形のままとするか、　「公開し、意見を募ります」と改めるか。②確定版で過去形に戻すか。第1章5は（1）アンケート調査から（7）計画の公表まで7項すべてが同じ書き方であるため、直す場合は7項をまとめて直すことになります</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
